--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-practitionerrole.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-practitionerrole.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>EU AI Act Human Overseer (PractitionerRole)</t>
+    <t>EU AI Practitioner Role</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:40:47+00:00</t>
+    <t>2026-06-18T12:04:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Defines the qualifications, specialty, and AI-specific training of the human responsible for oversight of the AI system, as required by the AI Act (HL-02).</t>
+    <t>A PractitionerRole profile representing the role, qualification context, specialty, and AI-related training information of the human reviewer involved in oversight of an AI-supported workflow.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -670,7 +670,7 @@
     <t>PractitionerRole.specialty</t>
   </si>
   <si>
-    <t>Clinical specialty (e.g., Radiology) required for oversight</t>
+    <t>Clinical specialty required for oversight</t>
   </si>
   <si>
     <t>The specialty of a practitioner that describes the functional role they are practicing at a given organization or location.</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-practitionerrole.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:04:51+00:00</t>
+    <t>2026-07-31T11:07:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -460,20 +460,20 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>PractitionerRole.extension:trainingFlag</t>
-  </si>
-  <si>
-    <t>trainingFlag</t>
+    <t>PractitionerRole.extension:trainingStatus</t>
+  </si>
+  <si>
+    <t>trainingStatus</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {http://example.org/fhir/eu-ai-transparency/StructureDefinition/ai-system-training-status}
 </t>
   </si>
   <si>
-    <t>Flag indicating system-specific training completed</t>
-  </si>
-  <si>
-    <t>Mandatory flag indicating whether the human actor has received specific training for the utilized AI tool.</t>
+    <t>Whether relevant AI training has been documented</t>
+  </si>
+  <si>
+    <t>Records whether the practitioner acting in the documented role has completed training specific to the relevant AI system.</t>
   </si>
   <si>
     <t>PractitionerRole.modifierExtension</t>
@@ -621,7 +621,7 @@
 </t>
   </si>
   <si>
-    <t>Organization responsible for the oversight process</t>
+    <t>Organization in which the practitioner performs the oversight role</t>
   </si>
   <si>
     <t>The organization where the Practitioner performs the roles associated.</t>
@@ -637,7 +637,7 @@
 </t>
   </si>
   <si>
-    <t>Specific role or seniority (e.g., Senior Physician, Medical Lead)</t>
+    <t>Professional role relevant to the human oversight activity</t>
   </si>
   <si>
     <t>Roles which this practitioner is authorized to perform for the organization.</t>
@@ -670,7 +670,7 @@
     <t>PractitionerRole.specialty</t>
   </si>
   <si>
-    <t>Clinical specialty required for oversight</t>
+    <t>Clinical specialty supporting competence for human oversight</t>
   </si>
   <si>
     <t>The specialty of a practitioner that describes the functional role they are practicing at a given organization or location.</t>
@@ -1146,9 +1146,9 @@
   <dimension ref="A1:AO25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="31.5625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="33.265625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="28.1953125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="11.9921875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>77</v>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>88</v>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-practitionerrole.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T11:07:29+00:00</t>
+    <t>2026-09-02T10:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-practitionerrole.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:48:14+00:00</t>
+    <t>2026-09-03T11:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-practitionerrole.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:53:05+00:00</t>
+    <t>2026-09-07T08:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
